--- a/data/trans_orig/Q45A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q45A_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2007</t>
+          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>29062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>17539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40441</t>
+          <t>39881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51782</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83381</t>
+          <t>82373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22262</t>
+          <t>21763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42760</t>
+          <t>43695</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78165</t>
+          <t>79430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117394</t>
+          <t>117445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>313526</t>
+          <t>314090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>367655</t>
+          <t>366679</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>292579</t>
+          <t>290906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>344817</t>
+          <t>343667</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>623053</t>
+          <t>624855</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>698908</t>
+          <t>699326</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>157380</t>
+          <t>163530</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>207152</t>
+          <t>209587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187346</t>
+          <t>186665</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234586</t>
+          <t>234806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359025</t>
+          <t>361761</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>425703</t>
+          <t>426728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68279</t>
+          <t>69232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104047</t>
+          <t>102874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98223</t>
+          <t>99077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136650</t>
+          <t>139417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179944</t>
+          <t>179191</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>230126</t>
+          <t>230672</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>36878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>26725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29607</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56938</t>
+          <t>57438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81379</t>
+          <t>81240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119853</t>
+          <t>121021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51609</t>
+          <t>52064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84267</t>
+          <t>86463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141632</t>
+          <t>140618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191469</t>
+          <t>193086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>444893</t>
+          <t>446855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>509693</t>
+          <t>510162</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>464070</t>
+          <t>466160</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>526482</t>
+          <t>527913</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>929714</t>
+          <t>928724</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1017183</t>
+          <t>1021240</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159209</t>
+          <t>161660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208559</t>
+          <t>210303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182479</t>
+          <t>183201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>234776</t>
+          <t>235231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>360520</t>
+          <t>357252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>431550</t>
+          <t>427451</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150185</t>
+          <t>149300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201396</t>
+          <t>197722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159239</t>
+          <t>158039</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209724</t>
+          <t>210917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>318855</t>
+          <t>319560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390030</t>
+          <t>394152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17653</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>29930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43501</t>
+          <t>43424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74522</t>
+          <t>73553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59293</t>
+          <t>59624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83360</t>
+          <t>84118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124893</t>
+          <t>122720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>260193</t>
+          <t>260125</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>312925</t>
+          <t>310372</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>241458</t>
+          <t>241625</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>291674</t>
+          <t>291755</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>515062</t>
+          <t>517499</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>589405</t>
+          <t>591367</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>125974</t>
+          <t>129150</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>168734</t>
+          <t>173790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131589</t>
+          <t>131817</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173528</t>
+          <t>172918</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>267961</t>
+          <t>269341</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>331202</t>
+          <t>331748</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155207</t>
+          <t>155608</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201374</t>
+          <t>200330</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186492</t>
+          <t>186427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>235681</t>
+          <t>236247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356308</t>
+          <t>354492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>420609</t>
+          <t>422374</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32592</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,47 +2828,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>36457</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>25822</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>51151</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>36457</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>25747</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>49751</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102446</t>
+          <t>102166</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142840</t>
+          <t>142576</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105147</t>
+          <t>104362</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144660</t>
+          <t>148269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>216422</t>
+          <t>218478</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>276306</t>
+          <t>276619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>426516</t>
+          <t>426039</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>489325</t>
+          <t>487376</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>514455</t>
+          <t>520657</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>581422</t>
+          <t>584029</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>967783</t>
+          <t>968876</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1053980</t>
+          <t>1050742</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>163321</t>
+          <t>166569</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>213137</t>
+          <t>213476</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>131951</t>
+          <t>131844</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>178664</t>
+          <t>177821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>308614</t>
+          <t>304996</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>373859</t>
+          <t>374517</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136452</t>
+          <t>137213</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>184094</t>
+          <t>183712</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>164342</t>
+          <t>164089</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>218326</t>
+          <t>213015</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>316066</t>
+          <t>317802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>382917</t>
+          <t>382046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52608</t>
+          <t>52802</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>86265</t>
+          <t>86352</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>42664</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72705</t>
+          <t>72172</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102408</t>
+          <t>101674</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>151091</t>
+          <t>148354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>303261</t>
+          <t>309197</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>378377</t>
+          <t>378323</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>239081</t>
+          <t>238811</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>300719</t>
+          <t>301688</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>565077</t>
+          <t>567074</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>655922</t>
+          <t>660112</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1503409</t>
+          <t>1504025</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1616120</t>
+          <t>1622779</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,82 +3701,82 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>49,54%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1633301</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>1579634</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1698815</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>48,33%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>46,75%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>50,27%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>3196122</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>3118734</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>3283400</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>48,03%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>46,86%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>49,34%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>1633301</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>1572951</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1689033</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>46,55%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>3140</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>3196122</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>3116389</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>3282669</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>48,03%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>46,83%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>660485</t>
+          <t>658849</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>755112</t>
+          <t>750555</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>674252</t>
+          <t>674272</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>771439</t>
+          <t>768681</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1364248</t>
+          <t>1356746</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1497118</t>
+          <t>1496805</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>551838</t>
+          <t>554201</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>640926</t>
+          <t>642961</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>651926</t>
+          <t>653794</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>746930</t>
+          <t>747492</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1229819</t>
+          <t>1230207</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1364749</t>
+          <t>1362563</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2012</t>
+          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2012 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27161</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65165</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55165</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73797</t>
+          <t>74763</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113413</t>
+          <t>113326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>234523</t>
+          <t>238054</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>288465</t>
+          <t>287705</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>210434</t>
+          <t>209198</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>261024</t>
+          <t>262435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>459787</t>
+          <t>462525</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>532284</t>
+          <t>532643</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>158734</t>
+          <t>156595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>205570</t>
+          <t>204232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169450</t>
+          <t>169295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216743</t>
+          <t>216884</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>343467</t>
+          <t>341002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>409944</t>
+          <t>412395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171126</t>
+          <t>172872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>220979</t>
+          <t>221643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193701</t>
+          <t>194369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243744</t>
+          <t>241281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379921</t>
+          <t>384065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>452409</t>
+          <t>455928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87436</t>
+          <t>86393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128830</t>
+          <t>129137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>58880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95706</t>
+          <t>95646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158576</t>
+          <t>160591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212927</t>
+          <t>216098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>301503</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>366829</t>
+          <t>364886</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>298004</t>
+          <t>296291</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>358100</t>
+          <t>355519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>616937</t>
+          <t>609716</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>704712</t>
+          <t>701698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198395</t>
+          <t>198497</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>255882</t>
+          <t>255436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>217640</t>
+          <t>219599</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>273733</t>
+          <t>275382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>434425</t>
+          <t>433075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>515804</t>
+          <t>515978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304546</t>
+          <t>302250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366631</t>
+          <t>364436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338625</t>
+          <t>338190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>404037</t>
+          <t>399882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>661037</t>
+          <t>661170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746206</t>
+          <t>749902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23633</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>18645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>38874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61167</t>
+          <t>63823</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98552</t>
+          <t>98201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54223</t>
+          <t>54713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>88036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125355</t>
+          <t>125169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174555</t>
+          <t>176505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>287350</t>
+          <t>288496</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>344363</t>
+          <t>343816</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>285206</t>
+          <t>287617</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>340755</t>
+          <t>340597</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>586861</t>
+          <t>587090</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>664174</t>
+          <t>669283</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>131526</t>
+          <t>131458</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177541</t>
+          <t>179335</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128136</t>
+          <t>129957</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>175259</t>
+          <t>175364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>272233</t>
+          <t>272724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>338293</t>
+          <t>337992</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170910</t>
+          <t>171355</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222979</t>
+          <t>222311</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204215</t>
+          <t>204812</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256001</t>
+          <t>258431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>392021</t>
+          <t>391595</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>461625</t>
+          <t>461771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31608</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31525</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28397</t>
+          <t>28963</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54817</t>
+          <t>55833</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97387</t>
+          <t>96925</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137876</t>
+          <t>138404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103972</t>
+          <t>104969</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145296</t>
+          <t>145038</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213099</t>
+          <t>213648</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>269913</t>
+          <t>272829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>352291</t>
+          <t>351488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>413475</t>
+          <t>417129</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>311661</t>
+          <t>307714</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>374800</t>
+          <t>369722</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>678244</t>
+          <t>681453</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>766294</t>
+          <t>767703</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137257</t>
+          <t>138604</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>185762</t>
+          <t>185173</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>185157</t>
+          <t>185579</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>238959</t>
+          <t>237569</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>334621</t>
+          <t>340446</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>405058</t>
+          <t>407560</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>235265</t>
+          <t>239733</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>295296</t>
+          <t>296579</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>325224</t>
+          <t>325376</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387306</t>
+          <t>388767</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>583130</t>
+          <t>584670</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>668767</t>
+          <t>673513</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44841</t>
+          <t>45442</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>77817</t>
+          <t>76989</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,82 +7117,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>50871</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>37474</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>65660</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>110039</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>91567</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>133298</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>50871</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>38429</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>68489</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>110039</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>89767</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>134096</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>322699</t>
+          <t>322808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>395535</t>
+          <t>395853</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>274890</t>
+          <t>276516</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>346754</t>
+          <t>345778</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>616885</t>
+          <t>615057</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>718600</t>
+          <t>717803</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1239377</t>
+          <t>1232426</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1352117</t>
+          <t>1354179</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1155578</t>
+          <t>1153347</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1274547</t>
+          <t>1273640</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2419586</t>
+          <t>2424562</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2583662</t>
+          <t>2590686</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>668943</t>
+          <t>673141</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>772726</t>
+          <t>773325</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>749702</t>
+          <t>748728</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>856074</t>
+          <t>852562</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1460157</t>
+          <t>1452745</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1603126</t>
+          <t>1589819</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>937676</t>
+          <t>936309</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1048680</t>
+          <t>1046832</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1114433</t>
+          <t>1115046</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1231370</t>
+          <t>1232402</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2084653</t>
+          <t>2096468</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2242736</t>
+          <t>2256729</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2016</t>
+          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>9625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62371</t>
+          <t>61716</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97304</t>
+          <t>96992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45712</t>
+          <t>45791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74418</t>
+          <t>73774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117481</t>
+          <t>118103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162930</t>
+          <t>162840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204241</t>
+          <t>209568</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>256879</t>
+          <t>260678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>148743</t>
+          <t>148877</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190918</t>
+          <t>195384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>369826</t>
+          <t>368443</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>434307</t>
+          <t>433626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>166024</t>
+          <t>163005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209868</t>
+          <t>211728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>207751</t>
+          <t>205369</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>257236</t>
+          <t>253326</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>384078</t>
+          <t>386849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>451395</t>
+          <t>453133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151732</t>
+          <t>148036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>197975</t>
+          <t>196319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179334</t>
+          <t>180480</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227131</t>
+          <t>228066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345427</t>
+          <t>339616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411390</t>
+          <t>412595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25366</t>
+          <t>25913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>122412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170332</t>
+          <t>170450</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85953</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123818</t>
+          <t>125701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220706</t>
+          <t>219756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>279261</t>
+          <t>280865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>322333</t>
+          <t>324142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>389264</t>
+          <t>387076</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>318971</t>
+          <t>322317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>380630</t>
+          <t>381229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>666063</t>
+          <t>658306</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>750816</t>
+          <t>751056</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>300741</t>
+          <t>299852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>362509</t>
+          <t>361206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>319158</t>
+          <t>315574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>380910</t>
+          <t>377179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>635636</t>
+          <t>636668</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>724285</t>
+          <t>730407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,42%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151534</t>
+          <t>151138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199597</t>
+          <t>200455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>208606</t>
+          <t>205852</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>264228</t>
+          <t>263689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>372294</t>
+          <t>372035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>449317</t>
+          <t>451403</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>24761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101364</t>
+          <t>103966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143012</t>
+          <t>146000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83442</t>
+          <t>86543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123086</t>
+          <t>124248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197249</t>
+          <t>197608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252008</t>
+          <t>251744</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>287901</t>
+          <t>286894</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>344527</t>
+          <t>344350</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>306178</t>
+          <t>304410</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>360505</t>
+          <t>362716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>612448</t>
+          <t>609742</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>687454</t>
+          <t>690900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154733</t>
+          <t>157034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203895</t>
+          <t>205581</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159093</t>
+          <t>159981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>205229</t>
+          <t>204788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>331576</t>
+          <t>330850</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>397141</t>
+          <t>400479</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116833</t>
+          <t>115397</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159926</t>
+          <t>158445</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132470</t>
+          <t>132688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>179550</t>
+          <t>177296</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>259934</t>
+          <t>258842</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>318765</t>
+          <t>319684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26039</t>
+          <t>26573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32027</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26068</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50153</t>
+          <t>51879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109443</t>
+          <t>111336</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152433</t>
+          <t>155172</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105007</t>
+          <t>106639</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>149704</t>
+          <t>150164</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>228852</t>
+          <t>227601</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>286129</t>
+          <t>288508</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>278072</t>
+          <t>278609</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>334594</t>
+          <t>334559</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>285901</t>
+          <t>284601</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>345622</t>
+          <t>344320</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>578624</t>
+          <t>579424</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>661084</t>
+          <t>664440</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>310377</t>
+          <t>309563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>368897</t>
+          <t>367385</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>312932</t>
+          <t>314759</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>376931</t>
+          <t>378346</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>643908</t>
+          <t>640798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>727802</t>
+          <t>725610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>120096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>167375</t>
+          <t>165196</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>210949</t>
+          <t>205952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>270471</t>
+          <t>265651</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>341056</t>
+          <t>342161</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>415646</t>
+          <t>414882</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47424</t>
+          <t>48318</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>32586</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62713</t>
+          <t>60391</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>63106</t>
+          <t>63286</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>99737</t>
+          <t>101169</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>434475</t>
+          <t>432886</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>517314</t>
+          <t>520029</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>352518</t>
+          <t>355870</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>428538</t>
+          <t>430403</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>813493</t>
+          <t>817359</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>929071</t>
+          <t>931540</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1155740</t>
+          <t>1153003</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1269485</t>
+          <t>1268164</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1111054</t>
+          <t>1109909</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1226141</t>
+          <t>1225604</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2290680</t>
+          <t>2299381</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2464298</t>
+          <t>2461245</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>983474</t>
+          <t>985807</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1089384</t>
+          <t>1096470</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1051775</t>
+          <t>1052092</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1161807</t>
+          <t>1166399</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2063623</t>
+          <t>2068231</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2227129</t>
+          <t>2225165</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>579940</t>
+          <t>583389</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>674326</t>
+          <t>674759</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>777964</t>
+          <t>774229</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>881380</t>
+          <t>880548</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1384503</t>
+          <t>1386881</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1523188</t>
+          <t>1527925</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q45A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q45A_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>28041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39881</t>
+          <t>39988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51346</t>
+          <t>51406</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82373</t>
+          <t>83322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21763</t>
+          <t>22890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43695</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79430</t>
+          <t>76953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117445</t>
+          <t>116352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>314090</t>
+          <t>313089</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>366679</t>
+          <t>366967</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>290906</t>
+          <t>294854</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>343667</t>
+          <t>344649</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>624855</t>
+          <t>620707</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>699326</t>
+          <t>694038</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>163530</t>
+          <t>158933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209587</t>
+          <t>207313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186665</t>
+          <t>186414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234806</t>
+          <t>234675</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361761</t>
+          <t>362466</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>426728</t>
+          <t>427025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69232</t>
+          <t>69749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102874</t>
+          <t>103790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99077</t>
+          <t>99207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139417</t>
+          <t>138372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179191</t>
+          <t>179017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>230672</t>
+          <t>231938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15967</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36878</t>
+          <t>38049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>29874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57438</t>
+          <t>56749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81240</t>
+          <t>79761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121021</t>
+          <t>117973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52064</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86463</t>
+          <t>85387</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140618</t>
+          <t>140489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193086</t>
+          <t>189782</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>446855</t>
+          <t>446038</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>510162</t>
+          <t>513247</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>466160</t>
+          <t>462266</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>527913</t>
+          <t>527031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>928724</t>
+          <t>927907</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1021240</t>
+          <t>1021498</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161660</t>
+          <t>161989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210303</t>
+          <t>208860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183201</t>
+          <t>181620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>235231</t>
+          <t>234548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357252</t>
+          <t>357527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>427451</t>
+          <t>430232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149300</t>
+          <t>148042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197722</t>
+          <t>198062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158039</t>
+          <t>159523</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210917</t>
+          <t>207546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>319560</t>
+          <t>317564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>394152</t>
+          <t>389443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29930</t>
+          <t>28090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43424</t>
+          <t>44748</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73553</t>
+          <t>75099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34099</t>
+          <t>35131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59624</t>
+          <t>61614</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84118</t>
+          <t>84698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122720</t>
+          <t>125198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>260125</t>
+          <t>257957</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310372</t>
+          <t>311527</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>241625</t>
+          <t>240133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>291755</t>
+          <t>292716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>517499</t>
+          <t>513376</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>591367</t>
+          <t>589459</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>129150</t>
+          <t>124479</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173790</t>
+          <t>169259</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131817</t>
+          <t>131205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172918</t>
+          <t>173962</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>269341</t>
+          <t>267922</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>331748</t>
+          <t>330413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155608</t>
+          <t>153982</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200330</t>
+          <t>203722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186427</t>
+          <t>186196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236247</t>
+          <t>235223</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>354492</t>
+          <t>354593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>422374</t>
+          <t>427399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25822</t>
+          <t>26002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51151</t>
+          <t>50564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102166</t>
+          <t>102081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142576</t>
+          <t>142514</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104362</t>
+          <t>104574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148269</t>
+          <t>144465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>218478</t>
+          <t>216818</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>276619</t>
+          <t>272518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>426039</t>
+          <t>425487</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>487376</t>
+          <t>489336</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>520657</t>
+          <t>520334</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>584029</t>
+          <t>581268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>968876</t>
+          <t>963607</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1050742</t>
+          <t>1056207</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>166569</t>
+          <t>165880</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>213476</t>
+          <t>215727</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>131844</t>
+          <t>131826</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177821</t>
+          <t>180208</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>304996</t>
+          <t>304837</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>374517</t>
+          <t>373737</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137213</t>
+          <t>138666</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>183712</t>
+          <t>184543</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>164089</t>
+          <t>163895</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>213015</t>
+          <t>214828</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317802</t>
+          <t>315825</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>382046</t>
+          <t>386592</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52802</t>
+          <t>54027</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>86561</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42664</t>
+          <t>42961</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72172</t>
+          <t>72004</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>101674</t>
+          <t>102298</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>148354</t>
+          <t>149196</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>309197</t>
+          <t>306719</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>378323</t>
+          <t>377718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>238811</t>
+          <t>238038</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>301688</t>
+          <t>301140</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>567074</t>
+          <t>568317</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>660112</t>
+          <t>664473</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1504025</t>
+          <t>1505457</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1622779</t>
+          <t>1622129</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1579634</t>
+          <t>1577997</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1698815</t>
+          <t>1692817</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3118734</t>
+          <t>3123025</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3283400</t>
+          <t>3280236</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>658849</t>
+          <t>659477</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>750555</t>
+          <t>753724</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>674272</t>
+          <t>678647</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>768681</t>
+          <t>772300</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1356746</t>
+          <t>1368145</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1496805</t>
+          <t>1500571</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>554201</t>
+          <t>551661</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>642961</t>
+          <t>641267</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>653794</t>
+          <t>653195</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>747492</t>
+          <t>746162</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1230207</t>
+          <t>1232305</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1362563</t>
+          <t>1359440</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68614</t>
+          <t>68774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30381</t>
+          <t>29544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>54556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74763</t>
+          <t>73933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113326</t>
+          <t>113602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>238054</t>
+          <t>235252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>287705</t>
+          <t>287427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>209198</t>
+          <t>208364</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>262435</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>462525</t>
+          <t>461392</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>532643</t>
+          <t>532844</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>156595</t>
+          <t>156348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>204232</t>
+          <t>208216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169295</t>
+          <t>168629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216884</t>
+          <t>217465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>341002</t>
+          <t>342675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>412395</t>
+          <t>410605</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172872</t>
+          <t>172321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221643</t>
+          <t>220471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194369</t>
+          <t>195050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>241281</t>
+          <t>244613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>384065</t>
+          <t>382398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>455928</t>
+          <t>450515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39077</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86393</t>
+          <t>90443</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129137</t>
+          <t>129153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58880</t>
+          <t>60037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95646</t>
+          <t>98063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160591</t>
+          <t>157817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216098</t>
+          <t>212296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301503</t>
+          <t>303338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>364886</t>
+          <t>364358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>296291</t>
+          <t>294775</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>355519</t>
+          <t>360469</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>609716</t>
+          <t>618299</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>701698</t>
+          <t>704318</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198497</t>
+          <t>199958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>255436</t>
+          <t>255138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>219599</t>
+          <t>220692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275382</t>
+          <t>276374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>433075</t>
+          <t>431973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>515978</t>
+          <t>510506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302250</t>
+          <t>304694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364436</t>
+          <t>366273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338190</t>
+          <t>338482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>399882</t>
+          <t>402333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>661170</t>
+          <t>659644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749902</t>
+          <t>746649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23863</t>
+          <t>23807</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38874</t>
+          <t>41184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63823</t>
+          <t>62943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98201</t>
+          <t>98666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54713</t>
+          <t>52276</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88036</t>
+          <t>84734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125169</t>
+          <t>127867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176505</t>
+          <t>175867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>288496</t>
+          <t>288723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>343816</t>
+          <t>344516</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>287617</t>
+          <t>285852</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>340597</t>
+          <t>342636</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>587090</t>
+          <t>589996</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>669283</t>
+          <t>671516</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>131458</t>
+          <t>132005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>179335</t>
+          <t>179776</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>129957</t>
+          <t>128986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>175364</t>
+          <t>177199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>272724</t>
+          <t>270814</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337992</t>
+          <t>337766</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>171355</t>
+          <t>169193</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222311</t>
+          <t>219905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204812</t>
+          <t>201791</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258431</t>
+          <t>257483</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>391595</t>
+          <t>390242</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>461771</t>
+          <t>463139</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30436</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30428</t>
+          <t>31172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28963</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55833</t>
+          <t>52633</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96925</t>
+          <t>97234</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138404</t>
+          <t>138499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104969</t>
+          <t>101426</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145038</t>
+          <t>143081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213648</t>
+          <t>210951</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>272829</t>
+          <t>271007</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>351488</t>
+          <t>353565</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>417129</t>
+          <t>413103</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>307714</t>
+          <t>312416</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>369722</t>
+          <t>371481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>681453</t>
+          <t>676422</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>767703</t>
+          <t>765653</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>138604</t>
+          <t>139708</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>185173</t>
+          <t>186463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>185579</t>
+          <t>183637</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>237569</t>
+          <t>235924</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>340446</t>
+          <t>337234</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>407560</t>
+          <t>407232</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>239733</t>
+          <t>238904</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>296579</t>
+          <t>295169</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>325376</t>
+          <t>324786</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>388767</t>
+          <t>389697</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>584670</t>
+          <t>583774</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>673513</t>
+          <t>670730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>44995</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76989</t>
+          <t>76022</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>37430</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65660</t>
+          <t>66521</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>91567</t>
+          <t>89566</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>133298</t>
+          <t>132809</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>322808</t>
+          <t>324371</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>395853</t>
+          <t>395262</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>276516</t>
+          <t>274789</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>345778</t>
+          <t>346179</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>615057</t>
+          <t>619935</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>717803</t>
+          <t>724255</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1232426</t>
+          <t>1236935</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1354179</t>
+          <t>1345481</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1153347</t>
+          <t>1160857</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1273640</t>
+          <t>1272280</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2424562</t>
+          <t>2424506</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2590686</t>
+          <t>2590359</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>673141</t>
+          <t>671925</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>773325</t>
+          <t>773772</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>748728</t>
+          <t>751048</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>852562</t>
+          <t>852164</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1452745</t>
+          <t>1457326</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1589819</t>
+          <t>1591093</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>936309</t>
+          <t>935696</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1046832</t>
+          <t>1048704</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1115046</t>
+          <t>1121387</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1232402</t>
+          <t>1237695</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2096468</t>
+          <t>2090214</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2256729</t>
+          <t>2238726</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9625</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>19967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61716</t>
+          <t>62618</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96992</t>
+          <t>97962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45791</t>
+          <t>46114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73774</t>
+          <t>75268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118103</t>
+          <t>116328</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162840</t>
+          <t>160345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>209568</t>
+          <t>207680</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>260678</t>
+          <t>255800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>148877</t>
+          <t>148868</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>195384</t>
+          <t>192506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>368443</t>
+          <t>369684</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>433626</t>
+          <t>434413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>163005</t>
+          <t>165353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>211728</t>
+          <t>211222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>205369</t>
+          <t>206310</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253326</t>
+          <t>256333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>386849</t>
+          <t>386052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>453133</t>
+          <t>451780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148036</t>
+          <t>150582</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196319</t>
+          <t>195313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180480</t>
+          <t>178548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>228066</t>
+          <t>227459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>339616</t>
+          <t>342792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>412595</t>
+          <t>413230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>18725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>25898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122412</t>
+          <t>124762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170450</t>
+          <t>169946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85697</t>
+          <t>86641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125701</t>
+          <t>125188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219756</t>
+          <t>218354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>280865</t>
+          <t>281591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>324142</t>
+          <t>322066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>387076</t>
+          <t>387586</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>322317</t>
+          <t>317739</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>381229</t>
+          <t>382404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>658306</t>
+          <t>661730</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>751056</t>
+          <t>751848</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>299852</t>
+          <t>300821</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>361206</t>
+          <t>361770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>315574</t>
+          <t>317089</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>377179</t>
+          <t>380722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>636668</t>
+          <t>638554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>730407</t>
+          <t>726306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151138</t>
+          <t>152201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200455</t>
+          <t>201318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205852</t>
+          <t>208232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>263689</t>
+          <t>264590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>372035</t>
+          <t>371718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>451403</t>
+          <t>448095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>9429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>21420</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>25837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103966</t>
+          <t>105145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146000</t>
+          <t>145326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86543</t>
+          <t>84998</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124248</t>
+          <t>121572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197608</t>
+          <t>196411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251744</t>
+          <t>254056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>286894</t>
+          <t>290368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>344350</t>
+          <t>345160</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>304410</t>
+          <t>299478</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>362716</t>
+          <t>357327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>609742</t>
+          <t>609105</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>690900</t>
+          <t>689838</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157034</t>
+          <t>155754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>205581</t>
+          <t>202584</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159981</t>
+          <t>160142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>204788</t>
+          <t>205703</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>330850</t>
+          <t>330876</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>400479</t>
+          <t>397590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115397</t>
+          <t>116012</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>158445</t>
+          <t>159303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132688</t>
+          <t>131964</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177296</t>
+          <t>176054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>258842</t>
+          <t>256963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>319684</t>
+          <t>322332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26573</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31759</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26212</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51879</t>
+          <t>49498</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111336</t>
+          <t>110686</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>155172</t>
+          <t>155400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>106639</t>
+          <t>106687</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150164</t>
+          <t>149733</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>227601</t>
+          <t>228007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288508</t>
+          <t>288446</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>278609</t>
+          <t>279681</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>334559</t>
+          <t>336234</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>284601</t>
+          <t>287471</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>344320</t>
+          <t>348861</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>579424</t>
+          <t>579638</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>664440</t>
+          <t>660906</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>309563</t>
+          <t>309892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>367385</t>
+          <t>367066</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>314759</t>
+          <t>313595</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>378346</t>
+          <t>376662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>640798</t>
+          <t>637927</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>725610</t>
+          <t>725176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>120096</t>
+          <t>119753</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>165196</t>
+          <t>166071</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>205952</t>
+          <t>208464</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>265651</t>
+          <t>263918</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>342161</t>
+          <t>341343</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>414882</t>
+          <t>416910</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48318</t>
+          <t>47286</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60391</t>
+          <t>62518</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>64204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101169</t>
+          <t>99811</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>432886</t>
+          <t>434504</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>520029</t>
+          <t>518520</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>355870</t>
+          <t>355156</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>430403</t>
+          <t>430717</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>817359</t>
+          <t>813106</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>931540</t>
+          <t>922519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1153003</t>
+          <t>1155608</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1268164</t>
+          <t>1267929</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1109909</t>
+          <t>1108549</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1225604</t>
+          <t>1220338</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2299381</t>
+          <t>2295800</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2461245</t>
+          <t>2459743</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>985807</t>
+          <t>980108</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1096470</t>
+          <t>1088890</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1052092</t>
+          <t>1047087</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1166399</t>
+          <t>1160649</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2068231</t>
+          <t>2064573</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2225165</t>
+          <t>2222941</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>583389</t>
+          <t>582874</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>674759</t>
+          <t>674582</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>774229</t>
+          <t>776187</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>880548</t>
+          <t>882238</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1386881</t>
+          <t>1381532</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1527925</t>
+          <t>1523051</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
